--- a/Data/EXCEL/Transfer/salemon/202208/8028-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8028-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8FBCD7E-9957-439F-AFF4-EE0699E37911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{062DA410-7A53-4A69-94CF-80E3DEE01690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8028-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,22 +1227,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q158"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="9.625" customWidth="1"/>
-    <col min="10" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
-    <col min="14" max="15" width="9.625" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.25" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1267,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1300,7 +1306,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1343,7 +1349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1382,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1541,7 +1547,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1594,7 +1600,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1647,7 +1653,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1806,7 +1812,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1859,7 +1865,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1965,7 +1971,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2018,7 +2024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2071,7 +2077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2124,7 +2130,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2177,7 +2183,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2230,7 +2236,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2283,7 +2289,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2336,7 +2342,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2389,7 +2395,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2442,7 +2448,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2495,7 +2501,7 @@
         <v>-7.8</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2548,7 +2554,7 @@
         <v>-9.1300000000000008</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2601,7 +2607,7 @@
         <v>-9.2100000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2654,7 +2660,7 @@
         <v>-9.49</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2707,7 +2713,7 @@
         <v>-8.7100000000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2760,7 +2766,7 @@
         <v>-6.69</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2813,7 +2819,7 @@
         <v>-3.72</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2866,7 +2872,7 @@
         <v>-0.56999999999999995</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2972,7 +2978,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3025,7 +3031,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3078,7 +3084,7 @@
         <v>-5.94</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3184,7 +3190,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3237,7 +3243,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3290,7 +3296,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3343,7 +3349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3396,7 +3402,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3449,7 +3455,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3502,7 +3508,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3555,7 +3561,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3608,7 +3614,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3661,7 +3667,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3714,7 +3720,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3767,7 +3773,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3873,7 +3879,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3926,7 +3932,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3979,7 +3985,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4032,7 +4038,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4191,7 +4197,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4244,7 +4250,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4297,7 +4303,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4350,7 +4356,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4403,7 +4409,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4456,7 +4462,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4509,7 +4515,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4562,7 +4568,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4615,7 +4621,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4668,7 +4674,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4721,7 +4727,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4774,7 +4780,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4827,7 +4833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4880,7 +4886,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4933,7 +4939,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4986,7 +4992,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5039,7 +5045,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5092,7 +5098,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5145,7 +5151,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5198,7 +5204,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5251,7 +5257,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5304,7 +5310,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5357,7 +5363,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5410,7 +5416,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5463,7 +5469,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5516,7 +5522,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5569,7 +5575,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5622,7 +5628,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5675,7 +5681,7 @@
         <v>-2.4500000000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5728,7 +5734,7 @@
         <v>-2.81</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5781,7 +5787,7 @@
         <v>-5.15</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5834,7 +5840,7 @@
         <v>-7.09</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5887,7 +5893,7 @@
         <v>-7.18</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5940,7 +5946,7 @@
         <v>-6.67</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5993,7 +5999,7 @@
         <v>-6.9</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6046,7 +6052,7 @@
         <v>-5.4</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6099,7 +6105,7 @@
         <v>-2.87</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>-3.56</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6205,7 +6211,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6258,7 +6264,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6311,7 +6317,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>39417</v>
       </c>
@@ -6364,7 +6370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>39387</v>
       </c>
@@ -6417,7 +6423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>39356</v>
       </c>
@@ -6470,7 +6476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>39326</v>
       </c>
@@ -6523,7 +6529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>39295</v>
       </c>
@@ -6576,7 +6582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>39264</v>
       </c>
@@ -6629,7 +6635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>39234</v>
       </c>
@@ -6682,7 +6688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>39203</v>
       </c>
@@ -6735,7 +6741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>39173</v>
       </c>
@@ -6788,7 +6794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>39142</v>
       </c>
@@ -6841,7 +6847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>39114</v>
       </c>
@@ -6894,7 +6900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>39083</v>
       </c>
@@ -6947,7 +6953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>39052</v>
       </c>
@@ -7000,7 +7006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>39022</v>
       </c>
@@ -7053,7 +7059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>38991</v>
       </c>
@@ -7106,7 +7112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>38961</v>
       </c>
@@ -7159,7 +7165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>38930</v>
       </c>
@@ -7212,7 +7218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>38899</v>
       </c>
@@ -7265,7 +7271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>38869</v>
       </c>
@@ -7318,7 +7324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>38838</v>
       </c>
@@ -7371,7 +7377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>38808</v>
       </c>
@@ -7424,7 +7430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>38777</v>
       </c>
@@ -7477,7 +7483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>38749</v>
       </c>
@@ -7530,7 +7536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>38718</v>
       </c>
@@ -7583,7 +7589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>38687</v>
       </c>
@@ -7636,7 +7642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>38657</v>
       </c>
@@ -7689,7 +7695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>38626</v>
       </c>
@@ -7742,7 +7748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>38596</v>
       </c>
@@ -7795,7 +7801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>38565</v>
       </c>
@@ -7848,7 +7854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>38534</v>
       </c>
@@ -7901,7 +7907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>38504</v>
       </c>
@@ -7954,7 +7960,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>38473</v>
       </c>
@@ -8007,7 +8013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>38443</v>
       </c>
@@ -8060,7 +8066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>38412</v>
       </c>
@@ -8113,7 +8119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>38384</v>
       </c>
@@ -8166,7 +8172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>38353</v>
       </c>
@@ -8219,7 +8225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>38322</v>
       </c>
@@ -8272,7 +8278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>38292</v>
       </c>
@@ -8325,7 +8331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>38261</v>
       </c>
@@ -8378,7 +8384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>38231</v>
       </c>
@@ -8431,7 +8437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>38200</v>
       </c>
@@ -8484,7 +8490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>38169</v>
       </c>
@@ -8537,7 +8543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>38139</v>
       </c>
@@ -8590,7 +8596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>38108</v>
       </c>
@@ -8643,7 +8649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>38078</v>
       </c>
@@ -8696,7 +8702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>38047</v>
       </c>
@@ -8749,7 +8755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>38018</v>
       </c>
@@ -8802,7 +8808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>37987</v>
       </c>
@@ -8855,7 +8861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>37956</v>
       </c>
@@ -8908,7 +8914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>37926</v>
       </c>
@@ -8961,7 +8967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>37895</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>37865</v>
       </c>
@@ -9067,7 +9073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>37834</v>
       </c>
@@ -9120,7 +9126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>37803</v>
       </c>
@@ -9173,7 +9179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>37773</v>
       </c>
@@ -9226,7 +9232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>37742</v>
       </c>
@@ -9279,7 +9285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>37712</v>
       </c>
@@ -9332,7 +9338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>37681</v>
       </c>
@@ -9385,7 +9391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>37653</v>
       </c>
@@ -9438,7 +9444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>37622</v>
       </c>
@@ -9491,7 +9497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>37591</v>
       </c>
@@ -9559,7 +9565,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>